--- a/assessment_forms/041_manual_handling_safety_assessment--assessment_forms.xlsx
+++ b/assessment_forms/041_manual_handling_safety_assessment--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>risk_factor_1</t>
+          <t>risk factor 1</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>risk_factor_2</t>
+          <t>risk factor 2</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>risk_factor_3</t>
+          <t>risk factor 3</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>risk_factor_4</t>
+          <t>risk factor 4</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>risk_factor_5</t>
+          <t>risk factor 5</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>risk_factor_6</t>
+          <t>risk factor 6</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>risk_factor_7</t>
+          <t>risk factor 7</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>risk_factor_8</t>
+          <t>risk factor 8</t>
         </is>
       </c>
     </row>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>risk_level_1</t>
+          <t>risk level 1</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>risk_level_2</t>
+          <t>risk level 2</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>risk_level_3</t>
+          <t>risk level 3</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>risk_level_4</t>
+          <t>risk level 4</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>risk_level_5</t>
+          <t>risk level 5</t>
         </is>
       </c>
     </row>
